--- a/p0930/file/score.xlsx
+++ b/p0930/file/score.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>신림고</t>
+          <t>구로고</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>신림고</t>
+          <t>구로고</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>신림고</t>
+          <t>구로고</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>신림고</t>
+          <t>구로고</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>신림고</t>
+          <t>구로고</t>
         </is>
       </c>
       <c r="D6" t="n">
